--- a/docs/test-cases/TC_Tahfidz_ImprovementBatas.xlsx
+++ b/docs/test-cases/TC_Tahfidz_ImprovementBatas.xlsx
@@ -687,7 +687,7 @@
       <c r="J2" s="2" t="inlineStr">
         <is>
           <t>Otomasi: Pengaturan/Kesiswaan/batas-tahfidz/hakakses.cy.js
-Run Cypress 6 Okt 2026 13:13 (staging 88e43584, akun QA BT): PASS (akun QA BT Semua: submenu tampil, Tambah &amp; Edit tersedia).
+Run Cypress 6 Okt 2026 13:13 (staging 88e43584, akun QA BT): PASS (akun QA BT Semua: submenu tampil, Tambah &amp; Edit tersedia). Retest Cypress 7 Okt 2026 (staging a9e3c84c, Chrome): PASS.
 Ref manual: IMT-001 (Pengaturan Batas Tahfidz; Scope Tiket; sumber E+P+D).</t>
         </is>
       </c>
@@ -732,13 +732,13 @@
       </c>
       <c r="I3" s="2" t="inlineStr">
         <is>
-          <t>FAIL</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="J3" s="2" t="inlineStr">
         <is>
           <t>Otomasi: Pengaturan/Kesiswaan/batas-tahfidz/hakakses.cy.js
-Run Cypress 6 Okt 2026 13:13 (staging 88e43584, akun QA BT): FAIL -&gt; BUG-016. Submenu tersembunyi (benar), tetapi halaman tetap bisa dibuka lewat URL langsung.
+Retest Cypress 7 Okt 2026 (staging a9e3c84c, Chrome): PASS -&gt; BUG-016 (celah URL) FIXED.
 Ref manual: IMT-002 (Pengaturan Batas Tahfidz; Scope Tiket; sumber P+D).</t>
         </is>
       </c>
@@ -789,7 +789,7 @@
       <c r="J4" s="2" t="inlineStr">
         <is>
           <t>Otomasi: Pengaturan/Kesiswaan/batas-tahfidz/hakakses.cy.js
-Run Cypress 6 Okt 2026 13:13 (staging 88e43584, akun QA BT): FAIL -&gt; BUG-016 (tombol Tambah tampil untuk akun Lihat).
+Retest Cypress 7 Okt 2026 (staging a9e3c84c, Chrome): FAIL -&gt; BUG-016 (Partially Fixed): aksi Lihat/Tambah/Ubah tidak dibangun (keputusan dev: fitur baru). Evidence docs/evidence/BUG-016/RETEST-2026-10-07_TC-IMT-003.png
 Form Jenis Pengguna V2 hanya punya checkbox on/off Batas Tahfidz (tanpa aksi Lihat/Tambah/Ubah) -&gt; diperkirakan FAIL (BUG-016).
 Ref manual: IMT-003 (Pengaturan Batas Tahfidz; Scope Tiket; sumber P+D).</t>
         </is>
@@ -841,7 +841,7 @@
       <c r="J5" s="2" t="inlineStr">
         <is>
           <t>Otomasi: Pengaturan/Kesiswaan/batas-tahfidz/hakakses.cy.js
-Run Cypress 6 Okt 2026 13:13 (staging 88e43584, akun QA BT): FAIL -&gt; BUG-016 (aksi Edit tampil untuk akun Lihat + Tambah).
+Retest Cypress 7 Okt 2026 (staging a9e3c84c, Chrome): FAIL -&gt; BUG-016 (Partially Fixed): aksi Lihat/Tambah/Ubah tidak dibangun (keputusan dev: fitur baru). Evidence docs/evidence/BUG-016/RETEST-2026-10-07_TC-IMT-004.png
 Form Jenis Pengguna V2 hanya punya checkbox on/off Batas Tahfidz (tanpa aksi Lihat/Tambah/Ubah) -&gt; diperkirakan FAIL (BUG-016).
 Ref manual: IMT-004 (Pengaturan Batas Tahfidz; Scope Tiket; sumber P+D).</t>
         </is>
@@ -893,7 +893,7 @@
       <c r="J6" s="2" t="inlineStr">
         <is>
           <t>Otomasi: Pengaturan/Kesiswaan/batas-tahfidz/hakakses.cy.js
-Run Cypress 6 Okt 2026 13:13 (staging 88e43584, akun QA BT): FAIL -&gt; BUG-016 (tombol Tambah tampil untuk akun Lihat + Ubah).
+Retest Cypress 7 Okt 2026 (staging a9e3c84c, Chrome): FAIL -&gt; BUG-016 (Partially Fixed): aksi Lihat/Tambah/Ubah tidak dibangun (keputusan dev: fitur baru). Evidence docs/evidence/BUG-016/RETEST-2026-10-07_TC-IMT-005.png
 Form Jenis Pengguna V2 hanya punya checkbox on/off Batas Tahfidz (tanpa aksi Lihat/Tambah/Ubah) -&gt; diperkirakan FAIL (BUG-016).
 Ref manual: IMT-005 (Pengaturan Batas Tahfidz; Scope Tiket; sumber P+D).</t>
         </is>
@@ -947,7 +947,7 @@
       <c r="J7" s="2" t="inlineStr">
         <is>
           <t>Otomasi: -
-Observasi lewat Claude in Chrome 6 Okt 2026: item Pengaturan &gt; Kesiswaan &gt; Batas Tahfidz hanya checkbox on/off, TIDAK ada aksi Semua/Lihat/Tambah/Ubah -&gt; BUG-016. Temuan UI form (counter/toggle tidak reaktif, judul modal Edit) -&gt; BUG-017.
+BUG-016 (Partially Fixed): form Jenis Pengguna tetap checkbox on/off tanpa aksi (keputusan dev 7 Okt 2026: fitur baru, bukan bug).
 Ref manual: IMT-006 (Pengaturan Batas Tahfidz; Scope Tiket; sumber P+D).</t>
         </is>
       </c>
@@ -998,7 +998,7 @@
       <c r="J8" s="2" t="inlineStr">
         <is>
           <t>Otomasi: Pengaturan/Kesiswaan/batas-tahfidz/pengaturanbatas.cy.js
-Run Cypress 6 Okt 2026 (staging 2a2a430e): PASS.
+Run Cypress 6 Okt 2026 (staging 2a2a430e): PASS. Retest Cypress 7 Okt 2026 (staging a9e3c84c, Chrome): PASS.
 Source V2 TahfidzLimit/Datatable: kolom Instansi, Batas Tahfidz, Metode Perhitungan Halaman, Dibuat Pada, Aksi; default sort created_at desc. Metode tampil '-' untuk Batas Juz/Surah.
 Ref manual: IMT-007 (Pengaturan Batas Tahfidz; Scope Tiket; sumber P).</t>
         </is>
@@ -1049,7 +1049,7 @@
       <c r="J9" s="2" t="inlineStr">
         <is>
           <t>Otomasi: Pengaturan/Kesiswaan/batas-tahfidz/pengaturanbatas.cy.js
-Run Cypress 6 Okt 2026 (staging 2a2a430e): PASS.
+Run Cypress 6 Okt 2026 (staging 2a2a430e): PASS. Retest Cypress 7 Okt 2026 (staging a9e3c84c, Chrome): PASS.
 Diuji lewat kombinasi filter yang tidak menghasilkan data (tanpa mengosongkan data bersama).
 Ref manual: IMT-008 (Pengaturan Batas Tahfidz; Scope Tiket; sumber P).</t>
         </is>
@@ -1102,7 +1102,7 @@
       <c r="J10" s="2" t="inlineStr">
         <is>
           <t>Otomasi: Pengaturan/Kesiswaan/batas-tahfidz/pengaturanbatas.cy.js
-Run Cypress 6 Okt 2026 (staging 2a2a430e): PASS.
+Run Cypress 6 Okt 2026 (staging 2a2a430e): PASS. Retest Cypress 7 Okt 2026 (staging a9e3c84c, Chrome): PASS.
 Source V2: filter 'Instansi' dan 'Batas Tahfidz' (rappasoft).
 Ref manual: IMT-009 (Pengaturan Batas Tahfidz; Scope Tiket; sumber P).</t>
         </is>
@@ -1154,7 +1154,7 @@
       <c r="J11" s="2" t="inlineStr">
         <is>
           <t>Otomasi: Pengaturan/Kesiswaan/batas-tahfidz/pengaturanbatas.cy.js
-Run Cypress 6 Okt 2026 (staging 2a2a430e): PASS.
+Run Cypress 6 Okt 2026 (staging 2a2a430e): PASS. Retest Cypress 7 Okt 2026 (staging a9e3c84c, Chrome): PASS.
 Ref manual: IMT-010 (Pengaturan Batas Tahfidz; Scope Tiket; sumber P).</t>
         </is>
       </c>
@@ -1256,7 +1256,7 @@
       <c r="J13" s="2" t="inlineStr">
         <is>
           <t>Otomasi: Pengaturan/Kesiswaan/batas-tahfidz/pengaturanbatas.cy.js
-Run Cypress 6 Okt 2026 (staging 2a2a430e) (11:30): FAIL -&gt; BUG-015 (evidence docs/evidence/BUG-015/). Simulasi tanpa menyimpan data: request digagalkan intercept / cookie sesi dihapus.
+Retest Cypress 7 Okt 2026 (staging a9e3c84c, Chrome): FAIL -&gt; BUG-015 (Partially Fixed). Offline: pesan + Coba Lagi tampil; setelah koneksi pulih banner &amp; Coba Lagi hilang, langkah 'pulihkan koneksi lalu klik Coba Lagi' tidak bisa. Evidence docs/evidence/BUG-015/RETEST-2026-10-07_TC-IMT-012.png
 Ref manual: IMT-012 (Pengaturan Batas Tahfidz; Negatif; sumber P).</t>
         </is>
       </c>
@@ -1312,7 +1312,7 @@
       <c r="J14" s="2" t="inlineStr">
         <is>
           <t>Otomasi: Pengaturan/Kesiswaan/batas-tahfidz/pengaturanbatas.cy.js
-Run Cypress 6 Okt 2026 (staging 2a2a430e): PASS.
+Run Cypress 6 Okt 2026 (staging 2a2a430e): PASS. Retest Cypress 7 Okt 2026 (staging a9e3c84c, Chrome): PASS.
 Source V2: dropdown Instansi = officesWithoutSetting(); default Batas = Halaman, Metode = mushaf; helper text sesuai blade.
 Ref manual: IMT-013 (Pengaturan Batas Tahfidz; Scope Tiket; sumber E+P).</t>
         </is>
@@ -1368,7 +1368,7 @@
       <c r="J15" s="2" t="inlineStr">
         <is>
           <t>Otomasi: Pengaturan/Kesiswaan/batas-tahfidz/pengaturanbatas.cy.js
-Run Cypress 6 Okt 2026 (staging 2a2a430e): PASS.
+Run Cypress 6 Okt 2026 (staging 2a2a430e): PASS. Retest Cypress 7 Okt 2026 (staging a9e3c84c, Chrome): PASS.
 Ref manual: IMT-014 (Pengaturan Batas Tahfidz; Scope Tiket; sumber E+P+D).</t>
         </is>
       </c>
@@ -1423,7 +1423,7 @@
       <c r="J16" s="2" t="inlineStr">
         <is>
           <t>Otomasi: Pengaturan/Kesiswaan/batas-tahfidz/pengaturanbatas.cy.js
-Run Cypress 6 Okt 2026 (staging 2a2a430e): PASS.
+Run Cypress 6 Okt 2026 (staging 2a2a430e): PASS. Retest Cypress 7 Okt 2026 (staging a9e3c84c, Chrome): PASS.
 Source V2: field Metode SELALU tampil &amp; wajib (sesuai keputusan PRD Flag no. 2).
 Ref manual: IMT-015 (Pengaturan Batas Tahfidz; Scope Tiket; sumber E+P+D).</t>
         </is>
@@ -1476,7 +1476,7 @@
       <c r="J17" s="2" t="inlineStr">
         <is>
           <t>Otomasi: Pengaturan/Kesiswaan/batas-tahfidz/pengaturanbatas.cy.js
-Run Cypress 6 Okt 2026 11:44 (staging 153647d9): PASS. Pengaturan dibuat untuk 'Digital International School' (office 69535bc689994b001aba0378) -&gt; HAPUS lewat DB (keputusan D1). Dicatat di docs/test-data/pengaturan-baru.json; run berikutnya tidak membuat lagi selama baris masih ada.
+Run Cypress 6 Okt 2026 11:44 (staging 153647d9): PASS. Pengaturan dibuat untuk 'Digital International School' (office 69535bc689994b001aba0378) -&gt; HAPUS lewat DB (keputusan D1). Dicatat di docs/test-data/pengaturan-baru.json; run berikutnya tidak membuat lagi selama baris masih ada. Run 7 Okt: di-skip otomatis (pengaturan dari run 6 Okt masih ada, menunggu dihapus lewat DB).
 Source V2: pesan 'Pengaturan Batas Tahfidz berhasil disimpan.' PERMANEN: tidak ada hapus pengaturan (lihat Pertanyaan QI).
 Ref manual: IMT-016 (Pengaturan Batas Tahfidz; Scope Tiket; sumber E+P+D).</t>
         </is>
@@ -1526,13 +1526,13 @@
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>FAIL</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
           <t>Otomasi: Pengaturan/Kesiswaan/batas-tahfidz/pengaturanbatas.cy.js
-Run Cypress 6 Okt 2026 (staging 2a2a430e): FAIL -&gt; BUG-014 (evidence docs/evidence/BUG-014/).
+Retest Cypress 7 Okt 2026 (staging a9e3c84c, Chrome): PASS -&gt; BUG-014 FIXED.
 Source V2: tombol Simpan TIDAK dinonaktifkan sebelum Instansi dipilih (x-buttons.submit tanpa :disabled); validasi server memakai pesan bawaan Laravel, bukan 'Lengkapi seluruh field yang wajib diisi.' -&gt; calon BUG.
 Ref manual: IMT-017 (Pengaturan Batas Tahfidz; Negatif; sumber P).</t>
         </is>
@@ -1585,7 +1585,7 @@
       <c r="J19" s="2" t="inlineStr">
         <is>
           <t>Otomasi: Pengaturan/Kesiswaan/batas-tahfidz/pengaturanbatas.cy.js
-Run Cypress 6 Okt 2026 11:44: PASS. Instansi QA &amp; instansi baru tidak ditawarkan; Simpan dari 'tab kedua' (opsi basi disisipkan) ditolak 'Instansi ini sudah memiliki pengaturan Batas Tahfidz.', tetap satu pengaturan.
+Run Cypress 6 Okt 2026 11:44: PASS. Instansi QA &amp; instansi baru tidak ditawarkan; Simpan dari 'tab kedua' (opsi basi disisipkan) ditolak 'Instansi ini sudah memiliki pengaturan Batas Tahfidz.', tetap satu pengaturan. Retest Cypress 7 Okt 2026 (staging a9e3c84c, Chrome): PASS.
 Ref manual: IMT-018 (Pengaturan Batas Tahfidz; Negatif; sumber P+D).</t>
         </is>
       </c>
@@ -1636,7 +1636,7 @@
       <c r="J20" s="2" t="inlineStr">
         <is>
           <t>Otomasi: Pengaturan/Kesiswaan/batas-tahfidz/hakakses.cy.js
-Run Cypress 6 Okt 2026 13:13 (staging 88e43584, akun QA BT): PASS dengan akun QA BT Semua (instansinya hanya SMP Digital Indonesia+ yang sudah berpengaturan): Tambah nonaktif + 'Seluruh instansi sudah memiliki pengaturan Batas Tahfidz.'
+Run Cypress 6 Okt 2026 13:13 (staging 88e43584, akun QA BT): PASS dengan akun QA BT Semua (instansinya hanya SMP Digital Indonesia+ yang sudah berpengaturan): Tambah nonaktif + 'Seluruh instansi sudah memiliki pengaturan Batas Tahfidz.' Retest Cypress 7 Okt 2026 (staging a9e3c84c, Chrome): PASS.
 Source V2: teks 'Seluruh instansi sudah memiliki pengaturan Batas Tahfidz.' + tombol disabled. Bergantung data seluruh instansi staging.
 Ref manual: IMT-019 (Pengaturan Batas Tahfidz; Negatif; sumber P).</t>
         </is>
@@ -1692,7 +1692,7 @@
       <c r="J21" s="2" t="inlineStr">
         <is>
           <t>Otomasi: Pengaturan/Kesiswaan/batas-tahfidz/pengaturanbatas.cy.js
-Run Cypress 6 Okt 2026 (staging 2a2a430e): PASS.
+Run Cypress 6 Okt 2026 (staging 2a2a430e): PASS. Retest Cypress 7 Okt 2026 (staging a9e3c84c, Chrome): PASS.
 Ref manual: IMT-020 (Pengaturan Batas Tahfidz; Scope Tiket; sumber P).</t>
         </is>
       </c>
@@ -1737,13 +1737,13 @@
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>FAIL</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
         <is>
           <t>Otomasi: Pengaturan/Kesiswaan/batas-tahfidz/pengaturanbatas.cy.js
-Run Cypress 6 Okt 2026 (staging 2a2a430e) (11:30): FAIL -&gt; BUG-015 (evidence docs/evidence/BUG-015/). Simulasi tanpa menyimpan data: request digagalkan intercept / cookie sesi dihapus. Bagian 'klik Simpan berkali-kali' belum diuji (butuh simpan sungguhan).
+Retest Cypress 7 Okt 2026 (staging a9e3c84c, Chrome): PASS -&gt; BUG-015 bagian gagal simpan FIXED (offline: pesan di modal, Simpan nonaktif, isian tetap).
 Ref manual: IMT-021 (Pengaturan Batas Tahfidz; Negatif; sumber P).</t>
         </is>
       </c>
@@ -1794,7 +1794,7 @@
       <c r="J23" s="2" t="inlineStr">
         <is>
           <t>Otomasi: Pengaturan/Kesiswaan/batas-tahfidz/pengaturanbatas.cy.js
-Run Cypress 6 Okt 2026 (staging 2a2a430e) (11:30): FAIL -&gt; BUG-015 (evidence docs/evidence/BUG-015/). Simulasi tanpa menyimpan data: request digagalkan intercept / cookie sesi dihapus. Redirect ke login sudah benar; teks notifikasi 'Sesi Anda Berakhir - Untuk keamanan akun, silakan login kembali.' berbeda dari PRD.
+Retest Cypress 7 Okt 2026 (staging a9e3c84c, Chrome): FAIL -&gt; BUG-015 (tidak diubah, keputusan dev): redirect login benar, teks 'Sesi Anda Berakhir' bukan versi PRD.
 Ref manual: IMT-022 (Pengaturan Batas Tahfidz; Negatif; sumber P).</t>
         </is>
       </c>
@@ -1850,7 +1850,7 @@
       <c r="J24" s="2" t="inlineStr">
         <is>
           <t>Otomasi: Pengaturan/Kesiswaan/batas-tahfidz/pengaturanbatas.cy.js
-Run Cypress 6 Okt 2026 (staging 2a2a430e): PASS.
+Run Cypress 6 Okt 2026 (staging 2a2a430e): PASS. Retest Cypress 7 Okt 2026 (staging a9e3c84c, Chrome): PASS.
 Source V2: pesan 'Perubahan pengaturan Batas Tahfidz berhasil disimpan.' Instansi tampil sebagai input disabled.
 Ref manual: IMT-023 (Pengaturan Batas Tahfidz; Scope Tiket; sumber E+P+D).</t>
         </is>
@@ -1906,7 +1906,7 @@
       <c r="J25" s="2" t="inlineStr">
         <is>
           <t>Otomasi: Pengaturan/Kesiswaan/batas-tahfidz/pengaturanbatas.cy.js
-Run Cypress 6 Okt 2026 (staging 2a2a430e): PASS.
+Run Cypress 6 Okt 2026 (staging 2a2a430e): PASS. Retest Cypress 7 Okt 2026 (staging a9e3c84c, Chrome): PASS.
 Ref manual: IMT-024 (Pengaturan Batas Tahfidz; Scope Tiket; sumber P).</t>
         </is>
       </c>
@@ -2012,7 +2012,7 @@
       <c r="J27" s="2" t="inlineStr">
         <is>
           <t>Otomasi: Pengaturan/Kesiswaan/batas-tahfidz/pengaturanbatas.cy.js
-Run Cypress 6 Okt 2026 (staging 2a2a430e): PASS.
+Run Cypress 6 Okt 2026 (staging 2a2a430e): PASS. Retest Cypress 7 Okt 2026 (staging a9e3c84c, Chrome): PASS.
 Ref manual: IMT-026 (Pengaturan Batas Tahfidz; Scope Tiket; sumber E+P+D).</t>
         </is>
       </c>
@@ -2060,15 +2060,15 @@
           <t>PRD</t>
         </is>
       </c>
-      <c r="I28" s="2" t="inlineStr">
-        <is>
-          <t>PASS</t>
+      <c r="I28" s="3" t="inlineStr">
+        <is>
+          <t>Blocked</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
         <is>
           <t>Otomasi: Pengaturan/Kesiswaan/batas-tahfidz/pengaturanbatas.cy.js
-Run Cypress 6 Okt 2026 (staging 2a2a430e): PASS.
+Run 7 Okt 2026: SMP Islam Terpadu Purwokerto kini punya pengaturan (insiden TC-IMT-022 versi lama menyimpan pengaturan) -&gt; hapus barisnya lewat DB (docs/test-data/pengaturan-baru.json). Sebelumnya PASS 6 Okt.
 Source V2: TahfidzUnit::defaultLimit -&gt; Halaman untuk Jenis Juz bila instansi tanpa pengaturan.
 Ref manual: IMT-027 (Pengaturan Batas Tahfidz; Scope Tiket; sumber P+D).</t>
         </is>
@@ -2124,7 +2124,7 @@
       <c r="J29" s="2" t="inlineStr">
         <is>
           <t>Otomasi: Kesiswaan/Tahfidz/improvement-batas/batasprogram.cy.js
-Run Cypress 6 Okt 2026 (staging 2a2a430e): PASS.
+Run Cypress 6 Okt 2026 (staging 2a2a430e): PASS. Retest Cypress 7 Okt 2026 (staging a9e3c84c, Chrome): PASS.
 Ref manual: IMT-028 (Batas Tahfidz pada Program (Tambah/Edit/Import Tahfidz); Scope Tiket; sumber E+P+D).</t>
         </is>
       </c>
@@ -2179,7 +2179,7 @@
       <c r="J30" s="2" t="inlineStr">
         <is>
           <t>Otomasi: Kesiswaan/Tahfidz/improvement-batas/batasprogram.cy.js
-Run Cypress 6 Okt 2026 (staging 2a2a430e): PASS.
+Run Cypress 6 Okt 2026 (staging 2a2a430e): PASS. Retest Cypress 7 Okt 2026 (staging a9e3c84c, Chrome): PASS.
 Source V2: TahfidzUnit::allowedLimits('juz') = juz, halaman, ayat.
 Ref manual: IMT-029 (Batas Tahfidz pada Program (Tambah/Edit/Import Tahfidz); Scope Tiket; sumber E+P).</t>
         </is>
@@ -2235,7 +2235,7 @@
       <c r="J31" s="2" t="inlineStr">
         <is>
           <t>Otomasi: Kesiswaan/Tahfidz/improvement-batas/batasprogram.cy.js
-Run Cypress 6 Okt 2026 (staging 2a2a430e): PASS.
+Run Cypress 6 Okt 2026 (staging 2a2a430e): PASS. Retest Cypress 7 Okt 2026 (staging a9e3c84c, Chrome): PASS.
 Source V2: allowedLimits('surah') = surah, ayat.
 Ref manual: IMT-030 (Batas Tahfidz pada Program (Tambah/Edit/Import Tahfidz); Scope Tiket; sumber E+P).</t>
         </is>
@@ -2291,7 +2291,7 @@
       <c r="J32" s="2" t="inlineStr">
         <is>
           <t>Otomasi: Kesiswaan/Tahfidz/improvement-batas/batasprogram.cy.js
-Run Cypress 6 Okt 2026 (staging 2a2a430e): PASS.
+Run Cypress 6 Okt 2026 (staging 2a2a430e): PASS. Retest Cypress 7 Okt 2026 (staging a9e3c84c, Chrome): PASS.
 Ref manual: IMT-031 (Batas Tahfidz pada Program (Tambah/Edit/Import Tahfidz); Scope Tiket; sumber P).</t>
         </is>
       </c>
@@ -2340,13 +2340,13 @@
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>FAIL</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
         <is>
           <t>Otomasi: Kesiswaan/Tahfidz/improvement-batas/batasprogram.cy.js
-Run Cypress 6 Okt 2026 (staging 2a2a430e): FAIL -&gt; BUG-011 (evidence docs/evidence/BUG-011/).
+Retest Cypress 7 Okt 2026 (staging a9e3c84c, Chrome): PASS -&gt; BUG-011 FIXED.
 Source V2: flash info 'Pilihan Batas Tahfidz disesuaikan karena Jenis Tahfidz diubah.'
 Ref manual: IMT-032 (Batas Tahfidz pada Program (Tambah/Edit/Import Tahfidz); Scope Tiket; sumber P).</t>
         </is>
@@ -2505,7 +2505,7 @@
       <c r="J36" s="2" t="inlineStr">
         <is>
           <t>Otomasi: Kesiswaan/Tahfidz/improvement-batas/batasprogram.cy.js
-Run Cypress 6 Okt 2026 (staging 2a2a430e): PASS.
+Run Cypress 6 Okt 2026 (staging 2a2a430e): PASS. Retest Cypress 7 Okt 2026 (staging a9e3c84c, Chrome): PASS.
 Ref manual: IMT-035 (Batas Tahfidz pada Program (Tambah/Edit/Import Tahfidz); Scope Tiket; sumber E+P+D).</t>
         </is>
       </c>
@@ -2561,7 +2561,7 @@
       <c r="J37" s="2" t="inlineStr">
         <is>
           <t>Otomasi: Kesiswaan/Tahfidz/improvement-batas/batasprogram.cy.js
-Run Cypress 6 Okt 2026 (staging 2a2a430e): PASS.
+Run Cypress 6 Okt 2026 (staging 2a2a430e): PASS. Retest Cypress 7 Okt 2026 (staging a9e3c84c, Chrome): PASS.
 Ref manual: IMT-036 (Batas Tahfidz pada Program (Tambah/Edit/Import Tahfidz); Scope Tiket; sumber E+P+D).</t>
         </is>
       </c>
@@ -2615,7 +2615,7 @@
       <c r="J38" s="2" t="inlineStr">
         <is>
           <t>Otomasi: Kesiswaan/Tahfidz/improvement-batas/batasprogram.cy.js
-Run Cypress 6 Okt 2026 (staging 2a2a430e): PASS.
+Run Cypress 6 Okt 2026 (staging 2a2a430e): PASS. Retest Cypress 7 Okt 2026 (staging a9e3c84c, Chrome): PASS.
 Source V2: teks 'Batas Tahfidz tidak dapat diubah karena program sudah memiliki riwayat progres.' (form-text text-warning).
 Ref manual: IMT-037 (Batas Tahfidz pada Program (Tambah/Edit/Import Tahfidz); Scope Tiket; sumber P).</t>
         </is>
@@ -2769,7 +2769,7 @@
       <c r="J41" s="2" t="inlineStr">
         <is>
           <t>Otomasi: Kesiswaan/Tahfidz/improvement-batas/detailprogram.cy.js
-Run Cypress 6 Okt 2026 (staging 2a2a430e): PASS.
+Run Cypress 6 Okt 2026 (staging 2a2a430e): PASS. Retest Cypress 7 Okt 2026 (staging a9e3c84c, Chrome): PASS.
 VERIFIED element analysis #1: nama program = &lt;a href=/student-affairs/tahfidz/detail/{id}&gt;.
 Ref manual: IMT-040 (Halaman Detail Program Tahfidz; Scope Tiket; sumber E+P+D).</t>
         </is>
@@ -2821,7 +2821,7 @@
       <c r="J42" s="2" t="inlineStr">
         <is>
           <t>Otomasi: Kesiswaan/Tahfidz/improvement-batas/detailprogram.cy.js
-Run Cypress 6 Okt 2026 (staging 2a2a430e): PASS.
+Run Cypress 6 Okt 2026 (staging 2a2a430e): PASS. Retest Cypress 7 Okt 2026 (staging a9e3c84c, Chrome): PASS.
 Ref manual: IMT-041 (Halaman Detail Program Tahfidz; Regresi; sumber E+P+D).</t>
         </is>
       </c>
@@ -2871,7 +2871,7 @@
       <c r="J43" s="2" t="inlineStr">
         <is>
           <t>Otomasi: Kesiswaan/Tahfidz/improvement-batas/detailprogram.cy.js
-Run Cypress 6 Okt 2026 (staging 2a2a430e): PASS.
+Run Cypress 6 Okt 2026 (staging 2a2a430e): PASS. Retest Cypress 7 Okt 2026 (staging a9e3c84c, Chrome): PASS.
 Ref manual: IMT-042 (Halaman Detail Program Tahfidz; Scope Tiket; sumber P).</t>
         </is>
       </c>
@@ -2922,7 +2922,7 @@
       <c r="J44" s="2" t="inlineStr">
         <is>
           <t>Otomasi: Kesiswaan/Tahfidz/improvement-batas/detailprogram.cy.js
-Run Cypress 6 Okt 2026 (staging 2a2a430e): PASS.
+Run Cypress 6 Okt 2026 (staging 2a2a430e): PASS. Retest Cypress 7 Okt 2026 (staging a9e3c84c, Chrome): PASS.
 List program V2: kolom checkbox belum terlihat di HTML element analysis #1 -&gt; cek saat element analysis.
 Ref manual: IMT-043 (Halaman Detail Program Tahfidz; Negatif; sumber P).</t>
         </is>
@@ -3023,7 +3023,7 @@
       <c r="J46" s="2" t="inlineStr">
         <is>
           <t>Otomasi: Kesiswaan/Tahfidz/improvement-batas/detailprogram.cy.js
-Run Cypress 6 Okt 2026 (staging 2a2a430e): PASS.
+Run Cypress 6 Okt 2026 (staging 2a2a430e): PASS. Retest Cypress 7 Okt 2026 (staging a9e3c84c, Chrome): PASS.
 VERIFIED element analysis #1: card info menampilkan 'Batas Tahfidz:' + badge.
 Ref manual: IMT-045 (Halaman Detail Program Tahfidz; Scope Tiket; sumber E+P).</t>
         </is>
@@ -3075,7 +3075,7 @@
       <c r="J47" s="2" t="inlineStr">
         <is>
           <t>Otomasi: Kesiswaan/Tahfidz/improvement-batas/detailprogram.cy.js
-Run Cypress 6 Okt 2026 12:05 (staging 88e43584): PASS dengan foto dummy cypress/fixtures/foto-siswa-qa.jpg (keputusan D4); foto dikembalikan ke avatar otomatis sesudahnya.
+Run Cypress 6 Okt 2026 12:05 (staging 88e43584): PASS dengan foto dummy cypress/fixtures/foto-siswa-qa.jpg (keputusan D4); foto dikembalikan ke avatar otomatis sesudahnya. Retest Cypress 7 Okt 2026 (staging a9e3c84c, Chrome): PASS.
 Source V2 member/table-row: foto symbol-35px symbol-circle; inisial bila tidak ada foto / onerror.
 Ref manual: IMT-046 (Halaman Detail Program Tahfidz; Scope Tiket; sumber E+P+D).</t>
         </is>
@@ -3126,7 +3126,7 @@
       <c r="J48" s="2" t="inlineStr">
         <is>
           <t>Otomasi: Kesiswaan/Tahfidz/improvement-batas/detailprogram.cy.js
-Run Cypress 6 Okt 2026 (staging 2a2a430e): PASS.
+Run Cypress 6 Okt 2026 (staging 2a2a430e): PASS. Retest Cypress 7 Okt 2026 (staging a9e3c84c, Chrome): PASS.
 Source V2: inisial 2 huruf pertama kata nama (sesuai keputusan PRD Flag no. 3).
 Ref manual: IMT-047 (Halaman Detail Program Tahfidz; Scope Tiket; sumber E+P+D).</t>
         </is>
@@ -3177,7 +3177,7 @@
       <c r="J49" s="2" t="inlineStr">
         <is>
           <t>Otomasi: Kesiswaan/Tahfidz/improvement-batas/detailprogram.cy.js
-Run Cypress 6 Okt 2026 12:05: PASS. Gambar digagalkan (cy.intercept 404, cache dimatikan) -&gt; inisial tampil.
+Run Cypress 6 Okt 2026 12:05: PASS. Gambar digagalkan (cy.intercept 404, cache dimatikan) -&gt; inisial tampil. Retest Cypress 7 Okt 2026 (staging a9e3c84c, Chrome): PASS.
 Diotomasi dengan cy.intercept gambar -&gt; 404 (onerror -&gt; inisial). Butuh anggota QA yang punya foto.
 Ref manual: IMT-048 (Halaman Detail Program Tahfidz; Negatif; sumber P).</t>
         </is>
@@ -3233,7 +3233,7 @@
       <c r="J50" s="2" t="inlineStr">
         <is>
           <t>Otomasi: Kesiswaan/Tahfidz/improvement-batas/detailprogram.cy.js
-Run Cypress 6 Okt 2026 (staging 2a2a430e): PASS.
+Run Cypress 6 Okt 2026 (staging 2a2a430e): PASS. Retest Cypress 7 Okt 2026 (staging a9e3c84c, Chrome): PASS.
 Ref manual: IMT-049 (Halaman Detail Program Tahfidz; Scope Tiket; sumber E+P+D).</t>
         </is>
       </c>
@@ -3287,7 +3287,7 @@
       <c r="J51" s="2" t="inlineStr">
         <is>
           <t>Otomasi: Kesiswaan/Tahfidz/improvement-batas/detailprogram.cy.js
-Run Cypress 6 Okt 2026 (staging 2a2a430e): PASS.
+Run Cypress 6 Okt 2026 (staging 2a2a430e): PASS. Retest Cypress 7 Okt 2026 (staging a9e3c84c, Chrome): PASS.
 DIKOREKSI dari testcase manual (40 -&gt; 41 halaman): Juz 3 = halaman 42-62, halaman 62 dimiliki Juz 3 &amp; Juz 4 (Mushaf Madinah).
 Ref manual: IMT-050 (Halaman Detail Program Tahfidz; Scope Tiket; sumber E+P+D).</t>
         </is>
@@ -3342,7 +3342,7 @@
       <c r="J52" s="2" t="inlineStr">
         <is>
           <t>Otomasi: Kesiswaan/Tahfidz/improvement-batas/detailprogram.cy.js
-Run Cypress 6 Okt 2026 (staging 2a2a430e): PASS.
+Run Cypress 6 Okt 2026 (staging 2a2a430e): PASS. Retest Cypress 7 Okt 2026 (staging a9e3c84c, Chrome): PASS.
 Ref manual: IMT-051 (Halaman Detail Program Tahfidz; Scope Tiket; sumber E+P+D).</t>
         </is>
       </c>
@@ -3396,7 +3396,7 @@
       <c r="J53" s="2" t="inlineStr">
         <is>
           <t>Otomasi: Kesiswaan/Tahfidz/improvement-batas/detailprogram.cy.js
-Run Cypress 6 Okt 2026 (staging 2a2a430e): PASS.
+Run Cypress 6 Okt 2026 (staging 2a2a430e): PASS. Retest Cypress 7 Okt 2026 (staging a9e3c84c, Chrome): PASS.
 Data disesuaikan: target D (78-82) tidak punya surah sebelum An-Naba', jadi 2 surah = An-Naba' + An-Nazi'at -&gt; posisi terakhir An-Nazi'at.
 Ref manual: IMT-052 (Halaman Detail Program Tahfidz; Scope Tiket; sumber E+P+D).</t>
         </is>
@@ -3451,7 +3451,7 @@
       <c r="J54" s="2" t="inlineStr">
         <is>
           <t>Otomasi: Kesiswaan/Tahfidz/improvement-batas/detailprogram.cy.js
-Run Cypress 6 Okt 2026 (staging 2a2a430e): PASS.
+Run Cypress 6 Okt 2026 (staging 2a2a430e): PASS. Retest Cypress 7 Okt 2026 (staging a9e3c84c, Chrome): PASS.
 Ref manual: IMT-053 (Halaman Detail Program Tahfidz; Scope Tiket; sumber E+P+D).</t>
         </is>
       </c>
@@ -3501,7 +3501,7 @@
       <c r="J55" s="2" t="inlineStr">
         <is>
           <t>Otomasi: Kesiswaan/Tahfidz/improvement-batas/detailprogram.cy.js
-Run Cypress 6 Okt 2026 (staging 2a2a430e): PASS.
+Run Cypress 6 Okt 2026 (staging 2a2a430e): PASS. Retest Cypress 7 Okt 2026 (staging a9e3c84c, Chrome): PASS.
 VERIFIED element analysis #1: '-' dan '0% (0 dari N satuan)'.
 Ref manual: IMT-054 (Halaman Detail Program Tahfidz; Scope Tiket; sumber P).</t>
         </is>
@@ -3557,7 +3557,7 @@
       <c r="J56" s="2" t="inlineStr">
         <is>
           <t>Otomasi: Kesiswaan/Tahfidz/improvement-batas/detailprogram.cy.js
-Run Cypress 6 Okt 2026 (staging 2a2a430e): PASS.
+Run Cypress 6 Okt 2026 (staging 2a2a430e): PASS. Retest Cypress 7 Okt 2026 (staging a9e3c84c, Chrome): PASS.
 Source V2: posisi terakhir = satuan TERJAUH (urutan mushaf) dari kumulatif riwayat terbaru (TahfidzUnit::lastUnit), bukan sekadar riwayat terakhir (Keputusan Flag no. 10).
 Ref manual: IMT-055 (Halaman Detail Program Tahfidz; Scope Tiket; sumber E+P+D).</t>
         </is>
@@ -3613,7 +3613,7 @@
       <c r="J57" s="2" t="inlineStr">
         <is>
           <t>Otomasi: Kesiswaan/Tahfidz/improvement-batas/detailprogram.cy.js
-Run Cypress 6 Okt 2026 (staging 2a2a430e): PASS.
+Run Cypress 6 Okt 2026 (staging 2a2a430e): PASS. Retest Cypress 7 Okt 2026 (staging a9e3c84c, Chrome): PASS.
 Ref manual: IMT-056 (Halaman Detail Program Tahfidz; Scope Tiket; sumber P+D).</t>
         </is>
       </c>
@@ -3662,13 +3662,13 @@
       </c>
       <c r="I58" s="2" t="inlineStr">
         <is>
-          <t>FAIL</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="J58" s="2" t="inlineStr">
         <is>
           <t>Otomasi: Kesiswaan/Tahfidz/improvement-batas/filterbatas.cy.js
-Run Cypress 6 Okt 2026 (staging 2a2a430e): FAIL -&gt; BUG-008 (evidence docs/evidence/BUG-008/).
+Retest Cypress 7 Okt 2026 (staging a9e3c84c, Chrome): PASS -&gt; BUG-008 FIXED.
 Ref manual: IMT-057 (Filter Batas Tahfidz (Detail Program); Scope Tiket; sumber E+P+D).</t>
         </is>
       </c>
@@ -3717,13 +3717,13 @@
       </c>
       <c r="I59" s="2" t="inlineStr">
         <is>
-          <t>FAIL</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="J59" s="2" t="inlineStr">
         <is>
           <t>Otomasi: Kesiswaan/Tahfidz/improvement-batas/filterbatas.cy.js
-Run Cypress 6 Okt 2026 (staging 2a2a430e): FAIL -&gt; BUG-008 (evidence docs/evidence/BUG-008/).
+Retest Cypress 7 Okt 2026 (staging a9e3c84c, Chrome): PASS -&gt; BUG-008 FIXED.
 Ref manual: IMT-058 (Filter Batas Tahfidz (Detail Program); Scope Tiket; sumber E+P+D).</t>
         </is>
       </c>
@@ -3772,13 +3772,13 @@
       </c>
       <c r="I60" s="2" t="inlineStr">
         <is>
-          <t>FAIL</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="J60" s="2" t="inlineStr">
         <is>
           <t>Otomasi: Kesiswaan/Tahfidz/improvement-batas/filterbatas.cy.js
-Run Cypress 6 Okt 2026 (staging 2a2a430e): FAIL -&gt; BUG-008 (evidence docs/evidence/BUG-008/).
+Retest Cypress 7 Okt 2026 (staging a9e3c84c, Chrome): PASS -&gt; BUG-008 FIXED.
 Ref manual: IMT-059 (Filter Batas Tahfidz (Detail Program); Scope Tiket; sumber E+P+D).</t>
         </is>
       </c>
@@ -3827,13 +3827,13 @@
       </c>
       <c r="I61" s="2" t="inlineStr">
         <is>
-          <t>FAIL</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="J61" s="2" t="inlineStr">
         <is>
           <t>Otomasi: Kesiswaan/Tahfidz/improvement-batas/filterbatas.cy.js
-Run Cypress 6 Okt 2026 (staging 2a2a430e): FAIL -&gt; BUG-008 (evidence docs/evidence/BUG-008/).
+Retest Cypress 7 Okt 2026 (staging a9e3c84c, Chrome): PASS -&gt; BUG-008 FIXED.
 Ref manual: IMT-060 (Filter Batas Tahfidz (Detail Program); Scope Tiket; sumber E+P+D).</t>
         </is>
       </c>
@@ -3881,13 +3881,13 @@
       </c>
       <c r="I62" s="2" t="inlineStr">
         <is>
-          <t>FAIL</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="J62" s="2" t="inlineStr">
         <is>
           <t>Otomasi: Kesiswaan/Tahfidz/improvement-batas/filterbatas.cy.js
-Run Cypress 6 Okt 2026 (staging 2a2a430e): FAIL -&gt; BUG-008 (evidence docs/evidence/BUG-008/).
+Retest Cypress 7 Okt 2026 (staging a9e3c84c, Chrome): PASS -&gt; BUG-008 FIXED.
 Source V2 MemberDatatable::memberIdsAtUnit: membandingkan lastUnit(unit_total) riwayat terbaru -&gt; sesuai expected.
 Ref manual: IMT-061 (Filter Batas Tahfidz (Detail Program); Negatif; sumber P).</t>
         </is>
@@ -3936,13 +3936,13 @@
       </c>
       <c r="I63" s="2" t="inlineStr">
         <is>
-          <t>FAIL</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="J63" s="2" t="inlineStr">
         <is>
           <t>Otomasi: Kesiswaan/Tahfidz/improvement-batas/filterbatas.cy.js
-Run Cypress 6 Okt 2026 (staging 2a2a430e): FAIL -&gt; BUG-013 (evidence docs/evidence/BUG-013/).
+Retest Cypress 7 Okt 2026 (staging a9e3c84c, Chrome): PASS -&gt; BUG-013 FIXED.
 Source V2 MemberDatatable::filters(): tingkat filter dengan SATU opsi TETAP ditampilkan (komentar kode bilang tidak ditawarkan, implementasi tidak) -&gt; calon BUG.
 Ref manual: IMT-062 (Filter Batas Tahfidz (Detail Program); Scope Tiket; sumber P).</t>
         </is>
@@ -3988,13 +3988,13 @@
       </c>
       <c r="I64" s="2" t="inlineStr">
         <is>
-          <t>FAIL</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="J64" s="2" t="inlineStr">
         <is>
           <t>Otomasi: Kesiswaan/Tahfidz/improvement-batas/filterbatas.cy.js
-Run Cypress 6 Okt 2026 (staging 2a2a430e): FAIL -&gt; BUG-008 (evidence docs/evidence/BUG-008/).
+Retest Cypress 7 Okt 2026 (staging a9e3c84c, Chrome): PASS -&gt; BUG-008 FIXED.
 Ref manual: IMT-063 (Filter Batas Tahfidz (Detail Program); Scope Tiket; sumber P).</t>
         </is>
       </c>
@@ -4040,13 +4040,13 @@
       </c>
       <c r="I65" s="2" t="inlineStr">
         <is>
-          <t>FAIL</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="J65" s="2" t="inlineStr">
         <is>
           <t>Otomasi: Kesiswaan/Tahfidz/improvement-batas/filterbatas.cy.js
-Run Cypress 6 Okt 2026 (staging 2a2a430e): FAIL -&gt; BUG-008 (evidence docs/evidence/BUG-008/).
+Retest Cypress 7 Okt 2026 (staging a9e3c84c, Chrome): PASS -&gt; BUG-008 FIXED.
 Source V2: export_table -&gt; exportToExcel() dari query datatable (crosschecked, ikut filter?).
 Ref manual: IMT-064 (Filter Batas Tahfidz (Detail Program); Scope Tiket; sumber P).</t>
         </is>
@@ -4102,7 +4102,7 @@
       <c r="J66" s="2" t="inlineStr">
         <is>
           <t>Otomasi: Kesiswaan/Tahfidz/improvement-batas/detailprogram.cy.js
-Run Cypress 6 Okt 2026 12:05: PASS dengan siswa staging #686 (keputusan D3/no.4); keanggotaan dihapus lagi sesudah test.
+Run Cypress 6 Okt 2026 12:05: PASS dengan siswa staging #686 (keputusan D3/no.4); keanggotaan dihapus lagi sesudah test. Retest Cypress 7 Okt 2026 (staging a9e3c84c, Chrome): PASS.
 DIKOREKSI dari testcase manual (40 -&gt; 41 halaman): Juz 3 = halaman 42-62, halaman 62 dimiliki Juz 3 &amp; Juz 4 (Mushaf Madinah).
 Ref manual: IMT-065 (Tambah Anggota; Scope Tiket; sumber P).</t>
         </is>
@@ -4153,7 +4153,7 @@
       <c r="J67" s="2" t="inlineStr">
         <is>
           <t>Otomasi: Kesiswaan/Tahfidz/improvement-batas/detailanggota.cy.js
-Run Cypress 6 Okt 2026 (staging 2a2a430e): PASS.
+Run Cypress 6 Okt 2026 (staging 2a2a430e): PASS. Retest Cypress 7 Okt 2026 (staging a9e3c84c, Chrome): PASS.
 Ref manual: IMT-066 (Halaman Detail Anggota Tahfidz; Scope Tiket; sumber E+P+D).</t>
         </is>
       </c>
@@ -4203,7 +4203,7 @@
       <c r="J68" s="2" t="inlineStr">
         <is>
           <t>Otomasi: Kesiswaan/Tahfidz/improvement-batas/detailanggota.cy.js
-Run Cypress 6 Okt 2026 (staging 2a2a430e): PASS.
+Run Cypress 6 Okt 2026 (staging 2a2a430e): PASS. Retest Cypress 7 Okt 2026 (staging a9e3c84c, Chrome): PASS.
 Ref manual: IMT-067 (Halaman Detail Anggota Tahfidz; Scope Tiket; sumber P).</t>
         </is>
       </c>
@@ -4253,7 +4253,7 @@
       <c r="J69" s="2" t="inlineStr">
         <is>
           <t>Otomasi: Kesiswaan/Tahfidz/improvement-batas/detailanggota.cy.js
-Run Cypress 6 Okt 2026 (staging 2a2a430e): PASS.
+Run Cypress 6 Okt 2026 (staging 2a2a430e): PASS. Retest Cypress 7 Okt 2026 (staging a9e3c84c, Chrome): PASS.
 Ref manual: IMT-068 (Halaman Detail Anggota Tahfidz; Regresi; sumber E+P+D).</t>
         </is>
       </c>
@@ -4303,7 +4303,7 @@
       <c r="J70" s="2" t="inlineStr">
         <is>
           <t>Otomasi: Kesiswaan/Tahfidz/improvement-batas/detailanggota.cy.js
-Run Cypress 6 Okt 2026 (staging 2a2a430e): PASS.
+Run Cypress 6 Okt 2026 (staging 2a2a430e): PASS. Retest Cypress 7 Okt 2026 (staging a9e3c84c, Chrome): PASS.
 Ref manual: IMT-069 (Halaman Detail Anggota Tahfidz; Scope Tiket; sumber P).</t>
         </is>
       </c>
@@ -4396,13 +4396,13 @@
       </c>
       <c r="I72" s="2" t="inlineStr">
         <is>
-          <t>FAIL</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="J72" s="2" t="inlineStr">
         <is>
           <t>Otomasi: Kesiswaan/Tahfidz/improvement-batas/detailanggota.cy.js
-Run Cypress 6 Okt 2026 (staging 2a2a430e): FAIL -&gt; BUG-012 (evidence docs/evidence/BUG-012/).
+Retest Cypress 7 Okt 2026 (staging a9e3c84c, Chrome): PASS -&gt; BUG-012 FIXED.
 VERIFIED element analysis #2: card Data Siswa V2 hanya Instansi, Nama, Tingkat-Kelas, Nama Program, Jenis, Target. TIDAK ada Batas Tahfidz -&gt; calon BUG.
 Ref manual: IMT-071 (Halaman Detail Anggota Tahfidz; Scope Tiket; sumber P).</t>
         </is>
@@ -4458,7 +4458,7 @@
       <c r="J73" s="2" t="inlineStr">
         <is>
           <t>Otomasi: Kesiswaan/Tahfidz/improvement-batas/formriwayat.cy.js
-Run Cypress 6 Okt 2026 (staging 2a2a430e): PASS.
+Run Cypress 6 Okt 2026 (staging 2a2a430e): PASS. Retest Cypress 7 Okt 2026 (staging a9e3c84c, Chrome): PASS.
 Ref manual: IMT-072 (Form Tambah Riwayat Progres; Scope Tiket; sumber E+P+D).</t>
         </is>
       </c>
@@ -4513,7 +4513,7 @@
       <c r="J74" s="2" t="inlineStr">
         <is>
           <t>Otomasi: Kesiswaan/Tahfidz/improvement-batas/formriwayat.cy.js
-Run Cypress 6 Okt 2026 (staging 2a2a430e): PASS.
+Run Cypress 6 Okt 2026 (staging 2a2a430e): PASS. Retest Cypress 7 Okt 2026 (staging a9e3c84c, Chrome): PASS.
 Ref manual: IMT-073 (Form Tambah Riwayat Progres; Scope Tiket; sumber E+P+D).</t>
         </is>
       </c>
@@ -4568,7 +4568,7 @@
       <c r="J75" s="2" t="inlineStr">
         <is>
           <t>Otomasi: Kesiswaan/Tahfidz/improvement-batas/formriwayat.cy.js
-Run Cypress 6 Okt 2026 (staging 2a2a430e): PASS.
+Run Cypress 6 Okt 2026 (staging 2a2a430e): PASS. Retest Cypress 7 Okt 2026 (staging a9e3c84c, Chrome): PASS.
 Ref manual: IMT-074 (Form Tambah Riwayat Progres; Scope Tiket; sumber E+P+D).</t>
         </is>
       </c>
@@ -4622,7 +4622,7 @@
       <c r="J76" s="2" t="inlineStr">
         <is>
           <t>Otomasi: Kesiswaan/Tahfidz/improvement-batas/formriwayat.cy.js
-Run Cypress 6 Okt 2026 (staging 2a2a430e): PASS.
+Run Cypress 6 Okt 2026 (staging 2a2a430e): PASS. Retest Cypress 7 Okt 2026 (staging a9e3c84c, Chrome): PASS.
 Ref manual: IMT-075 (Form Tambah Riwayat Progres; Scope Tiket; sumber E+P).</t>
         </is>
       </c>
@@ -4677,7 +4677,7 @@
       <c r="J77" s="2" t="inlineStr">
         <is>
           <t>Otomasi: Kesiswaan/Tahfidz/improvement-batas/formriwayat.cy.js
-Run Cypress 6 Okt 2026 (staging 2a2a430e): PASS.
+Run Cypress 6 Okt 2026 (staging 2a2a430e): PASS. Retest Cypress 7 Okt 2026 (staging a9e3c84c, Chrome): PASS.
 Ref manual: IMT-076 (Form Tambah Riwayat Progres; Scope Tiket; sumber E+P).</t>
         </is>
       </c>
@@ -4732,7 +4732,7 @@
       <c r="J78" s="2" t="inlineStr">
         <is>
           <t>Otomasi: Kesiswaan/Tahfidz/improvement-batas/formriwayat.cy.js
-Run Cypress 6 Okt 2026 (staging 2a2a430e): PASS.
+Run Cypress 6 Okt 2026 (staging 2a2a430e): PASS. Retest Cypress 7 Okt 2026 (staging a9e3c84c, Chrome): PASS.
 DIKOREKSI dari testcase manual (40 -&gt; 41 halaman): Juz 3 = halaman 42-62, halaman 62 dimiliki Juz 3 &amp; Juz 4 (Mushaf Madinah).
 Ref manual: IMT-077 (Form Tambah Riwayat Progres; Scope Tiket; sumber E+P+D).</t>
         </is>
@@ -4788,7 +4788,7 @@
       <c r="J79" s="2" t="inlineStr">
         <is>
           <t>Otomasi: Kesiswaan/Tahfidz/improvement-batas/formriwayat.cy.js
-Run Cypress 6 Okt 2026 (staging 2a2a430e): PASS.
+Run Cypress 6 Okt 2026 (staging 2a2a430e): PASS. Retest Cypress 7 Okt 2026 (staging a9e3c84c, Chrome): PASS.
 Ref manual: IMT-078 (Form Tambah Riwayat Progres; Scope Tiket; sumber E+P+D).</t>
         </is>
       </c>
@@ -4843,7 +4843,7 @@
       <c r="J80" s="2" t="inlineStr">
         <is>
           <t>Otomasi: Kesiswaan/Tahfidz/improvement-batas/formriwayat.cy.js
-Run Cypress 6 Okt 2026 (staging 2a2a430e): PASS.
+Run Cypress 6 Okt 2026 (staging 2a2a430e): PASS. Retest Cypress 7 Okt 2026 (staging a9e3c84c, Chrome): PASS.
 Ref manual: IMT-079 (Form Tambah Riwayat Progres; Scope Tiket; sumber E+P+D).</t>
         </is>
       </c>
@@ -4897,7 +4897,7 @@
       <c r="J81" s="2" t="inlineStr">
         <is>
           <t>Otomasi: Kesiswaan/Tahfidz/improvement-batas/formriwayat.cy.js
-Run Cypress 6 Okt 2026 (staging 2a2a430e): PASS.
+Run Cypress 6 Okt 2026 (staging 2a2a430e): PASS. Retest Cypress 7 Okt 2026 (staging a9e3c84c, Chrome): PASS.
 Source V2: langkah dengan satu opsi dipilih otomatis &amp; disembunyikan (visibleSteps).
 Ref manual: IMT-080 (Form Tambah Riwayat Progres; Scope Tiket; sumber E+P+D).</t>
         </is>
@@ -4953,7 +4953,7 @@
       <c r="J82" s="2" t="inlineStr">
         <is>
           <t>Otomasi: Kesiswaan/Tahfidz/improvement-batas/formriwayat.cy.js
-Run Cypress 6 Okt 2026 (staging 2a2a430e): PASS.
+Run Cypress 6 Okt 2026 (staging 2a2a430e): PASS. Retest Cypress 7 Okt 2026 (staging a9e3c84c, Chrome): PASS.
 Ref manual: IMT-081 (Form Tambah Riwayat Progres; Negatif; sumber E+P+D).</t>
         </is>
       </c>
@@ -5008,7 +5008,7 @@
       <c r="J83" s="2" t="inlineStr">
         <is>
           <t>Otomasi: Kesiswaan/Tahfidz/improvement-batas/formriwayat.cy.js
-Run Cypress 6 Okt 2026 (staging 2a2a430e): PASS.
+Run Cypress 6 Okt 2026 (staging 2a2a430e): PASS. Retest Cypress 7 Okt 2026 (staging a9e3c84c, Chrome): PASS.
 Source V2: pilihan yang tidak lagi tersedia dibuang; yang masih sah dipertahankan (tiket Multi Select Q7).
 Ref manual: IMT-082 (Form Tambah Riwayat Progres; Scope Tiket; sumber P).</t>
         </is>
@@ -5064,7 +5064,7 @@
       <c r="J84" s="2" t="inlineStr">
         <is>
           <t>Otomasi: Kesiswaan/Tahfidz/improvement-batas/formriwayat.cy.js
-Run Cypress 6 Okt 2026 (staging 2a2a430e): PASS.
+Run Cypress 6 Okt 2026 (staging 2a2a430e): PASS. Retest Cypress 7 Okt 2026 (staging a9e3c84c, Chrome): PASS.
 Ref manual: IMT-083 (Form Tambah Riwayat Progres; Scope Tiket; sumber E+P+D).</t>
         </is>
       </c>
@@ -5119,7 +5119,7 @@
       <c r="J85" s="2" t="inlineStr">
         <is>
           <t>Otomasi: Kesiswaan/Tahfidz/improvement-batas/formriwayat.cy.js
-Run Cypress 6 Okt 2026 (staging 2a2a430e): PASS.
+Run Cypress 6 Okt 2026 (staging 2a2a430e): PASS. Retest Cypress 7 Okt 2026 (staging a9e3c84c, Chrome): PASS.
 DIKOREKSI dari testcase manual (40 -&gt; 41 halaman): Juz 3 = halaman 42-62, halaman 62 dimiliki Juz 3 &amp; Juz 4 (Mushaf Madinah).
 Ref manual: IMT-084 (Form Tambah Riwayat Progres; Scope Tiket; sumber E+P+D).</t>
         </is>
@@ -5175,7 +5175,7 @@
       <c r="J86" s="2" t="inlineStr">
         <is>
           <t>Otomasi: Kesiswaan/Tahfidz/improvement-batas/formriwayat.cy.js
-Run Cypress 6 Okt 2026 (staging 2a2a430e): PASS.
+Run Cypress 6 Okt 2026 (staging 2a2a430e): PASS. Retest Cypress 7 Okt 2026 (staging a9e3c84c, Chrome): PASS.
 Ref manual: IMT-085 (Form Tambah Riwayat Progres; Scope Tiket; sumber P+D).</t>
         </is>
       </c>
@@ -5230,7 +5230,7 @@
       <c r="J87" s="2" t="inlineStr">
         <is>
           <t>Otomasi: Kesiswaan/Tahfidz/improvement-batas/formriwayat.cy.js
-Run Cypress 6 Okt 2026 (staging 2a2a430e): PASS.
+Run Cypress 6 Okt 2026 (staging 2a2a430e): PASS. Retest Cypress 7 Okt 2026 (staging a9e3c84c, Chrome): PASS.
 Ref manual: IMT-086 (Form Tambah Riwayat Progres; Scope Tiket; sumber E+P).</t>
         </is>
       </c>
@@ -5281,7 +5281,7 @@
       <c r="J88" s="2" t="inlineStr">
         <is>
           <t>Otomasi: Kesiswaan/Tahfidz/improvement-batas/formriwayat.cy.js
-Run Cypress 6 Okt 2026 (staging 2a2a430e): PASS.
+Run Cypress 6 Okt 2026 (staging 2a2a430e): PASS. Retest Cypress 7 Okt 2026 (staging a9e3c84c, Chrome): PASS.
 Source V2: 'Pilih minimal satu satuan yang sudah hafal.' (sama dengan tiket Multi Select TC-077).
 Ref manual: IMT-087 (Form Tambah Riwayat Progres; Negatif; sumber P).</t>
         </is>
@@ -5336,7 +5336,7 @@
       <c r="J89" s="2" t="inlineStr">
         <is>
           <t>Otomasi: Kesiswaan/Tahfidz/improvement-batas/formriwayat.cy.js
-Run Cypress 6 Okt 2026 (staging 2a2a430e): PASS.
+Run Cypress 6 Okt 2026 (staging 2a2a430e): PASS. Retest Cypress 7 Okt 2026 (staging a9e3c84c, Chrome): PASS.
 Ref manual: IMT-088 (Form Tambah Riwayat Progres; Scope Tiket; sumber P).</t>
         </is>
       </c>
@@ -5392,7 +5392,7 @@
       <c r="J90" s="2" t="inlineStr">
         <is>
           <t>Otomasi: Kesiswaan/Tahfidz/improvement-batas/formriwayat.cy.js
-Run Cypress 6 Okt 2026 (staging 2a2a430e): PASS.
+Run Cypress 6 Okt 2026 (staging 2a2a430e): PASS. Retest Cypress 7 Okt 2026 (staging a9e3c84c, Chrome): PASS.
 Ref manual: IMT-089 (Form Tambah Riwayat Progres; Scope Tiket; sumber E+P+D).</t>
         </is>
       </c>
@@ -5447,7 +5447,7 @@
       <c r="J91" s="2" t="inlineStr">
         <is>
           <t>Otomasi: Kesiswaan/Tahfidz/improvement-batas/formriwayat.cy.js
-Run Cypress 6 Okt 2026 (staging 2a2a430e): PASS.
+Run Cypress 6 Okt 2026 (staging 2a2a430e): PASS. Retest Cypress 7 Okt 2026 (staging a9e3c84c, Chrome): PASS.
 DIKOREKSI dari testcase manual (40 -&gt; 41 halaman): Juz 3 = halaman 42-62, halaman 62 dimiliki Juz 3 &amp; Juz 4 (Mushaf Madinah).
 Ref manual: IMT-090 (Form Tambah Riwayat Progres; Scope Tiket; sumber E+P+D).</t>
         </is>
@@ -5503,7 +5503,7 @@
       <c r="J92" s="2" t="inlineStr">
         <is>
           <t>Otomasi: Kesiswaan/Tahfidz/improvement-batas/formriwayat.cy.js
-Run Cypress 6 Okt 2026 (staging 2a2a430e): PASS.
+Run Cypress 6 Okt 2026 (staging 2a2a430e): PASS. Retest Cypress 7 Okt 2026 (staging a9e3c84c, Chrome): PASS.
 Ref manual: IMT-091 (Form Tambah Riwayat Progres; Scope Tiket; sumber E+P+D).</t>
         </is>
       </c>
@@ -5558,7 +5558,7 @@
       <c r="J93" s="2" t="inlineStr">
         <is>
           <t>Otomasi: Kesiswaan/Tahfidz/improvement-batas/formriwayat.cy.js
-Run Cypress 6 Okt 2026 (staging 2a2a430e): PASS.
+Run Cypress 6 Okt 2026 (staging 2a2a430e): PASS. Retest Cypress 7 Okt 2026 (staging a9e3c84c, Chrome): PASS.
 Source V2 Helpers::formatPercentage: non-bulat -&gt; 2 desimal titik ('7.50% (3 dari 40 halaman)').
 DIKOREKSI dari testcase manual (40 -&gt; 41 halaman): Juz 3 = halaman 42-62, halaman 62 dimiliki Juz 3 &amp; Juz 4 (Mushaf Madinah).
 Ref manual: IMT-092 (Form Tambah Riwayat Progres; Scope Tiket; sumber P).</t>
@@ -5615,7 +5615,7 @@
       <c r="J94" s="2" t="inlineStr">
         <is>
           <t>Otomasi: Kesiswaan/Tahfidz/improvement-batas/riwayatbatas.cy.js
-Run Cypress 6 Okt 2026 (staging 2a2a430e): PASS.
+Run Cypress 6 Okt 2026 (staging 2a2a430e): PASS. Retest Cypress 7 Okt 2026 (staging a9e3c84c, Chrome): PASS.
 Ref manual: IMT-093 (Form Edit Riwayat Progres; Scope Tiket; sumber E+P+D).</t>
         </is>
       </c>
@@ -5670,7 +5670,7 @@
       <c r="J95" s="2" t="inlineStr">
         <is>
           <t>Otomasi: Kesiswaan/Tahfidz/improvement-batas/riwayatbatas.cy.js
-Run Cypress 6 Okt 2026 (staging 2a2a430e): PASS.
+Run Cypress 6 Okt 2026 (staging 2a2a430e): PASS. Retest Cypress 7 Okt 2026 (staging a9e3c84c, Chrome): PASS.
 Ref manual: IMT-094 (Form Edit Riwayat Progres; Scope Tiket; sumber E+P+D).</t>
         </is>
       </c>
@@ -5719,13 +5719,13 @@
       </c>
       <c r="I96" s="2" t="inlineStr">
         <is>
-          <t>FAIL</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="J96" s="2" t="inlineStr">
         <is>
           <t>Otomasi: Kesiswaan/Tahfidz/improvement-batas/riwayatbatas.cy.js
-Run Cypress 6 Okt 2026 (staging 2a2a430e): FAIL -&gt; BUG-007. List riwayat &amp; pencapaian riwayat benar (80%); baris anggota di Detail Program tampil '-' / 0%.
+Retest Cypress 7 Okt 2026 (staging a9e3c84c, Chrome): PASS -&gt; BUG-007 FIXED.
 Ref manual: IMT-095 (Form Edit Riwayat Progres; Scope Tiket; sumber E+P+D).</t>
         </is>
       </c>
@@ -5780,7 +5780,7 @@
       <c r="J97" s="2" t="inlineStr">
         <is>
           <t>Otomasi: Kesiswaan/Tahfidz/improvement-batas/riwayatbatas.cy.js
-Run Cypress 6 Okt 2026 (staging 2a2a430e): PASS.
+Run Cypress 6 Okt 2026 (staging 2a2a430e): PASS. Retest Cypress 7 Okt 2026 (staging a9e3c84c, Chrome): PASS.
 Ref manual: IMT-096 (List dan Export Riwayat Progres; Scope Tiket; sumber E+P).</t>
         </is>
       </c>
@@ -5831,7 +5831,7 @@
       <c r="J98" s="2" t="inlineStr">
         <is>
           <t>Otomasi: Kesiswaan/Tahfidz/improvement-batas/riwayatbatas.cy.js
-Run Cypress 6 Okt 2026 (staging 2a2a430e): PASS.
+Run Cypress 6 Okt 2026 (staging 2a2a430e): PASS. Retest Cypress 7 Okt 2026 (staging a9e3c84c, Chrome): PASS.
 Ref manual: IMT-097 (List dan Export Riwayat Progres; Scope Tiket; sumber P).</t>
         </is>
       </c>
@@ -5880,13 +5880,13 @@
       </c>
       <c r="I99" s="2" t="inlineStr">
         <is>
-          <t>FAIL</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="J99" s="2" t="inlineStr">
         <is>
           <t>Otomasi: Kesiswaan/Tahfidz/improvement-batas/riwayatbatas.cy.js
-Run Cypress 6 Okt 2026 (staging 2a2a430e) (11:30): FAIL -&gt; BUG-009 (riwayat pertama di tanggal sama tampil 80%, expected 60% — keputusan dev B1: urut tanggal lalu id). Juga terdampak BUG-007 (baris anggota Detail Program '-').
+Retest Cypress 7 Okt 2026 (staging a9e3c84c, Chrome): PASS -&gt; BUG-007 &amp; BUG-009 FIXED.
 Ref manual: IMT-098 (List dan Export Riwayat Progres; Scope Tiket; sumber P).</t>
         </is>
       </c>
@@ -5937,7 +5937,7 @@
       <c r="J100" s="2" t="inlineStr">
         <is>
           <t>Otomasi: Kesiswaan/Tahfidz/improvement-batas/detailanggota.cy.js
-Run Cypress 6 Okt 2026 (staging 2a2a430e): PASS.
+Run Cypress 6 Okt 2026 (staging 2a2a430e): PASS. Retest Cypress 7 Okt 2026 (staging a9e3c84c, Chrome): PASS.
 VERIFIED element analysis #2 (F): kolom Capaian = posisi (div.fw-bold) + progress bar + '0% (0 dari N satuan)'.
 DIKOREKSI dari testcase manual (40 -&gt; 41 halaman): Juz 3 = halaman 42-62, halaman 62 dimiliki Juz 3 &amp; Juz 4 (Mushaf Madinah).
 Ref manual: IMT-099 (Detail Siswa - Tab Tahfidz; Scope Tiket; sumber P).</t>
@@ -5989,7 +5989,7 @@
       <c r="J101" s="2" t="inlineStr">
         <is>
           <t>Otomasi: Kesiswaan/Tahfidz/improvement-batas/detailanggota.cy.js
-Run Cypress 6 Okt 2026 (staging 2a2a430e): PASS.
+Run Cypress 6 Okt 2026 (staging 2a2a430e): PASS. Retest Cypress 7 Okt 2026 (staging a9e3c84c, Chrome): PASS.
 Ref manual: IMT-100 (Detail Siswa - Tab Tahfidz; Scope Tiket; sumber P).</t>
         </is>
       </c>
@@ -6044,7 +6044,7 @@
       <c r="J102" s="2" t="inlineStr">
         <is>
           <t>Otomasi: Kesiswaan/Tahfidz/improvement-batas/mushaf.cy.js
-Run Cypress 6 Okt 2026 (staging 2a2a430e): PASS.
+Run Cypress 6 Okt 2026 (staging 2a2a430e): PASS. Retest Cypress 7 Okt 2026 (staging a9e3c84c, Chrome): PASS.
 Source V2: peta halaman 604 halaman, 665 baris (docs/tahfidz_batas_tahfidz.md). Dijalankan pada Program U #247 (target Juz 1-30) karena Program F hanya Juz 30; form dibuka tanpa disimpan.
 Ref manual: IMT-101 (Perilaku Umum; Scope Tiket; sumber E+P+D).</t>
         </is>
@@ -6096,7 +6096,7 @@
       <c r="J103" s="2" t="inlineStr">
         <is>
           <t>Otomasi: Kesiswaan/Tahfidz/improvement-batas/mushaf.cy.js
-Run Cypress 6 Okt 2026 (staging 2a2a430e): PASS.
+Run Cypress 6 Okt 2026 (staging 2a2a430e): PASS. Retest Cypress 7 Okt 2026 (staging a9e3c84c, Chrome): PASS.
 Data disesuaikan: tidak ada program QA bertarget Al-Baqarah -&gt; dicek Al-Mulk 30 ayat &amp; An-Naba' 40 ayat (Program E), serta 37 surah Juz 30 (Program C).
 Ref manual: IMT-102 (Perilaku Umum; Scope Tiket; sumber E+P+D).</t>
         </is>
@@ -6248,13 +6248,13 @@
       </c>
       <c r="I106" s="2" t="inlineStr">
         <is>
-          <t>FAIL</t>
+          <t>Skip (Won't Fix)</t>
         </is>
       </c>
       <c r="J106" s="2" t="inlineStr">
         <is>
           <t>Otomasi: Kesiswaan/Tahfidz/improvement-batas/mushaf.cy.js
-Run Cypress 6 Okt 2026 (staging 2a2a430e): FAIL -&gt; BUG-010. Screenshot yang sama juga memperlihatkan BUG-009 (riwayat pertama di tanggal sama ikut 2 dari 23).
+BUG-010 Won't Fix (keputusan dev 7 Okt 2026, known limitation; fix butuh migrasi). Spec it.skip, assertion PRD disimpan.
 Source V2: achievement_display memformat halaman memakai metode instansi SAAT INI (formatPageParts), sehingga riwayat lama ikut berubah tampilan setelah metode diganti -&gt; calon BUG / PRD-ambigu.
 Ref manual: IMT-105 (Perilaku Umum; Scope Tiket; sumber P+D).</t>
         </is>
